--- a/doc/Gantt_Sprint_Rivano.xlsx
+++ b/doc/Gantt_Sprint_Rivano.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cp-24tom\3eme_Annee\Codage\Car_Rental\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A28614-98FF-4081-9DCC-C71E1968FE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DE901E-AD0D-4C16-9E32-3F5CCE58EC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Avancement" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="64">
   <si>
     <t>RIVANO - Avancement du sprint</t>
   </si>
@@ -133,33 +133,15 @@
     <t>Ecran d'accueil et de liste selon la maquette</t>
   </si>
   <si>
-    <t>Tests unitaires Jest (8 fichiers fromJson)</t>
-  </si>
-  <si>
-    <t>Review avec M. Guerdat</t>
-  </si>
-  <si>
     <t>Rattrapage du CIE - module ICH-335</t>
   </si>
   <si>
-    <t>Recuperation et rangement des assets (logos marques)</t>
-  </si>
-  <si>
-    <t>Bottom sheet + filtres (type de voiture, slider prix)</t>
-  </si>
-  <si>
     <t>En cours</t>
   </si>
   <si>
     <t>Decoupage de l'ecran liste en widgets separes</t>
   </si>
   <si>
-    <t>Mise a jour de la documentation</t>
-  </si>
-  <si>
-    <t>Brancher les filtres sur la liste</t>
-  </si>
-  <si>
     <t>A faire</t>
   </si>
   <si>
@@ -197,13 +179,73 @@
   </si>
   <si>
     <t>3h55</t>
+  </si>
+  <si>
+    <t>Mise a jour : 11/09/2026 (fin du sprint)</t>
+  </si>
+  <si>
+    <t>lu 07/09</t>
+  </si>
+  <si>
+    <t>je 10/09</t>
+  </si>
+  <si>
+    <t>ve 11/09</t>
+  </si>
+  <si>
+    <t>4h30</t>
+  </si>
+  <si>
+    <t>en cours</t>
+  </si>
+  <si>
+    <t>Tests unitaires (9 Jest serveur + 8 fromJson Flutter)</t>
+  </si>
+  <si>
+    <t>Reviews avec M. Guerdat</t>
+  </si>
+  <si>
+    <t>Recuperation et rangement des assets (photos, logos)</t>
+  </si>
+  <si>
+    <t>Bottom sheet de filtres : type de voiture + slider prix</t>
+  </si>
+  <si>
+    <t>Rental Time + calendrier (1er essai abandonne)</t>
+  </si>
+  <si>
+    <t>Rental Time : choix Heure / Jour (min. 1 heure)</t>
+  </si>
+  <si>
+    <t>Filtres Car location, Rating, Seating, Fuel type</t>
+  </si>
+  <si>
+    <t>Filtres fonctionnels (Provider Riverpod)</t>
+  </si>
+  <si>
+    <t>Section Brands (ListView.builder)</t>
+  </si>
+  <si>
+    <t>Prise en main du Mac + mise a jour macOS 26.6.2</t>
+  </si>
+  <si>
+    <t>Installation Xcode 26.6 (Intel) + import du projet</t>
+  </si>
+  <si>
+    <t>Documentation + Gantt de fin de sprint</t>
+  </si>
+  <si>
+    <t>Gestion des erreurs reseau cote client</t>
+  </si>
+  <si>
+    <t>Build et test sur iPhone depuis le Mac</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,20 +295,10 @@
       <name val="Arial"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -302,7 +334,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -325,20 +357,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD7D7D7"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -362,12 +385,9 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -393,13 +413,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>318277</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>36634</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>360943</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>186753</xdr:rowOff>
@@ -793,39 +813,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:U39"/>
+  <dimension ref="B1:Q42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="52" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="12" width="10" customWidth="1"/>
+    <col min="4" max="16" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:17" ht="18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B2" s="2"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-    </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-    </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
+      <c r="D1" s="18"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+    </row>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="20" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -853,32 +875,41 @@
         <v>10</v>
       </c>
       <c r="L4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>13</v>
@@ -887,13 +918,22 @@
         <v>12</v>
       </c>
       <c r="L5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="P5" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
@@ -910,10 +950,13 @@
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
-    </row>
-    <row r="7" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
-        <v>46</v>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+    </row>
+    <row r="7" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>16</v>
@@ -928,16 +971,11 @@
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="21"/>
-    </row>
-    <row r="8" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+    </row>
+    <row r="8" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>17</v>
       </c>
@@ -954,16 +992,11 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
-    </row>
-    <row r="9" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+    </row>
+    <row r="9" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>18</v>
       </c>
@@ -980,18 +1013,14 @@
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
-      <c r="N9" s="21" t="e" vm="1">
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="19" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="21"/>
-    </row>
-    <row r="10" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>19</v>
       </c>
@@ -1008,16 +1037,11 @@
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="21"/>
-      <c r="S10" s="21"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="21"/>
-    </row>
-    <row r="11" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+    </row>
+    <row r="11" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>20</v>
       </c>
@@ -1034,16 +1058,11 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-    </row>
-    <row r="12" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row r="12" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>21</v>
       </c>
@@ -1060,16 +1079,11 @@
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="21"/>
-    </row>
-    <row r="13" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+    </row>
+    <row r="13" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>23</v>
       </c>
@@ -1086,16 +1100,11 @@
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-    </row>
-    <row r="14" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+    </row>
+    <row r="14" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>24</v>
       </c>
@@ -1112,16 +1121,11 @@
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-    </row>
-    <row r="15" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+    </row>
+    <row r="15" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>25</v>
       </c>
@@ -1138,16 +1142,11 @@
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-    </row>
-    <row r="16" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+    </row>
+    <row r="16" spans="2:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>26</v>
       </c>
@@ -1164,16 +1163,11 @@
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-    </row>
-    <row r="17" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+    </row>
+    <row r="17" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>27</v>
       </c>
@@ -1190,18 +1184,13 @@
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-    </row>
-    <row r="18" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+    </row>
+    <row r="18" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>16</v>
@@ -1216,18 +1205,13 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-    </row>
-    <row r="19" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+    </row>
+    <row r="19" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>16</v>
@@ -1240,20 +1224,15 @@
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
+      <c r="L19" s="7"/>
       <c r="M19" s="8"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-    </row>
-    <row r="20" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+    </row>
+    <row r="20" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>16</v>
@@ -1268,47 +1247,37 @@
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-    </row>
-    <row r="21" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+    </row>
+    <row r="21" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="11"/>
+      <c r="I21" s="7"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-    </row>
-    <row r="22" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+    </row>
+    <row r="22" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -1316,25 +1285,20 @@
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="8"/>
       <c r="M22" s="8"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-    </row>
-    <row r="23" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+    </row>
+    <row r="23" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -1343,50 +1307,40 @@
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="8"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-    </row>
-    <row r="24" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+    </row>
+    <row r="24" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-    </row>
-    <row r="25" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+    </row>
+    <row r="25" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -1397,22 +1351,17 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-    </row>
-    <row r="26" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M25" s="7"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+    </row>
+    <row r="26" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
@@ -1423,22 +1372,17 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-    </row>
-    <row r="27" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M26" s="7"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+    </row>
+    <row r="27" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -1449,14 +1393,17 @@
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-    </row>
-    <row r="28" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M27" s="7"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+    </row>
+    <row r="28" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
@@ -1467,56 +1414,203 @@
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B30" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-    </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B31" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B32" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="19"/>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="19"/>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="17"/>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="17"/>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="17"/>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="17"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="10"/>
+    </row>
+    <row r="29" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+    </row>
+    <row r="30" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+    </row>
+    <row r="31" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+    </row>
+    <row r="32" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="11"/>
+    </row>
+    <row r="33" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="11"/>
+    </row>
+    <row r="34" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="11"/>
+    </row>
+    <row r="35" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="11"/>
+    </row>
+    <row r="36" spans="2:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="11"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B40" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B41" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B42" s="16" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
